--- a/Employee_Reports_wi48/Dushan Priyankara Herath Herath Mudiyanselage Q0578.xlsx
+++ b/Employee_Reports_wi48/Dushan Priyankara Herath Herath Mudiyanselage Q0578.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-68</v>
+        <v>-71</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-60</v>
+        <v>-63</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-59</v>
+        <v>-62</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-55</v>
+        <v>-58</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-46</v>
+        <v>-49</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-48</v>
+        <v>-51</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-34</v>
+        <v>-37</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-61</v>
+        <v>-64</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-41</v>
+        <v>-44</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-284</v>
+        <v>-287</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1265,11 +1265,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-382</v>
+        <v>-385</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1314,11 +1314,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-405</v>
+        <v>-408</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-347</v>
+        <v>-350</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1400,11 +1400,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-347</v>
+        <v>-350</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1437,11 +1437,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-119</v>
+        <v>-122</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1486,11 +1486,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-119</v>
+        <v>-122</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1535,11 +1535,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-144</v>
+        <v>-147</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1584,11 +1584,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-15</v>
+        <v>-18</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1633,11 +1633,11 @@
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -1682,11 +1682,11 @@
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -1731,11 +1731,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1780,11 +1780,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1817,11 +1817,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1866,11 +1866,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1903,11 +1903,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
